--- a/RESERACH/REPORT/latest codex/Book3 (version 1).xlsx
+++ b/RESERACH/REPORT/latest codex/Book3 (version 1).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris\Desktop\Amazon-FBA-Agent-System-v32 - latest good - Copy (8) - Copy - Copy - POSTLONGRUNPREKIRO2 beforecompletion-\RESERACH\REPORT\latest codex\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DFD7143-71DB-4718-93A5-6D50A24ADCAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F29636B-8AC7-4E01-839D-8F4A7FC053A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="390" windowWidth="28815" windowHeight="14460" activeTab="1" xr2:uid="{5455FC11-1847-42A2-B519-762328C97C89}"/>
+    <workbookView xWindow="0" yWindow="1740" windowWidth="28800" windowHeight="14460" activeTab="1" xr2:uid="{5455FC11-1847-42A2-B519-762328C97C89}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -6159,7 +6159,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="561" row="1">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="1">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -55145,7 +55145,6 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{395C1DF4-F46F-462D-BCBE-A54EF9178E28}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:AE33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -55244,7 +55243,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:31" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>11179760954</v>
       </c>
@@ -55529,7 +55528,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="5" spans="1:31" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>5030481981234</v>
       </c>
@@ -55620,7 +55619,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="6" spans="1:31" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>28503059141</v>
       </c>
@@ -55716,7 +55715,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="7" spans="1:31" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5015302107291</v>
       </c>
@@ -55812,7 +55811,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="8" spans="1:31" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>5010792424811</v>
       </c>
@@ -55908,7 +55907,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="9" spans="1:31" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:31" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>5030481930331</v>
       </c>
@@ -55998,7 +55997,7 @@
         <v>1231</v>
       </c>
     </row>
-    <row r="10" spans="1:31" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:31" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>5010792424804</v>
       </c>
@@ -56093,7 +56092,7 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="11" spans="1:31" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:31" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>5027148067165</v>
       </c>
@@ -56186,7 +56185,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="12" spans="1:31" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:31" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>5030481800368</v>
       </c>
@@ -56279,7 +56278,7 @@
         <v>1304</v>
       </c>
     </row>
-    <row r="13" spans="1:31" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:31" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>5038673181646</v>
       </c>
@@ -56461,7 +56460,7 @@
         <v>1452</v>
       </c>
     </row>
-    <row r="15" spans="1:31" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:31" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>5015302203511</v>
       </c>
@@ -56743,7 +56742,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="18" spans="1:31" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:31" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>5030481800351</v>
       </c>
@@ -56836,7 +56835,7 @@
         <v>1547</v>
       </c>
     </row>
-    <row r="19" spans="1:31" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:31" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>5030481800351</v>
       </c>
@@ -56929,7 +56928,7 @@
         <v>1547</v>
       </c>
     </row>
-    <row r="20" spans="1:31" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:31" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>5055441459684</v>
       </c>
@@ -57022,7 +57021,7 @@
         <v>1644</v>
       </c>
     </row>
-    <row r="21" spans="1:31" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:31" ht="45" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>5055441459684</v>
       </c>
@@ -57115,7 +57114,7 @@
         <v>1644</v>
       </c>
     </row>
-    <row r="22" spans="1:31" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:31" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>5030481943034</v>
       </c>
@@ -57208,7 +57207,7 @@
         <v>1651</v>
       </c>
     </row>
-    <row r="23" spans="1:31" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:31" ht="45" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>11179050857</v>
       </c>
@@ -57304,7 +57303,7 @@
         <v>1704</v>
       </c>
     </row>
-    <row r="24" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>5050565294555</v>
       </c>
@@ -57398,7 +57397,7 @@
         <v>1758</v>
       </c>
     </row>
-    <row r="25" spans="1:31" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:31" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>5038673184722</v>
       </c>
@@ -57766,7 +57765,7 @@
         <v>1850</v>
       </c>
     </row>
-    <row r="29" spans="1:31" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:31" ht="45" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>5030481943065</v>
       </c>
@@ -57857,7 +57856,7 @@
         <v>1857</v>
       </c>
     </row>
-    <row r="30" spans="1:31" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:31" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>5052578010603</v>
       </c>
@@ -57948,7 +57947,7 @@
         <v>1864</v>
       </c>
     </row>
-    <row r="31" spans="1:31" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:31" ht="45" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>5030481930133</v>
       </c>
@@ -58041,7 +58040,7 @@
         <v>1871</v>
       </c>
     </row>
-    <row r="32" spans="1:31" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:31" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>5030481930010</v>
       </c>
@@ -58132,7 +58131,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="33" spans="1:31" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:31" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>11179500307</v>
       </c>
@@ -58229,18 +58228,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AE33" xr:uid="{395C1DF4-F46F-462D-BCBE-A54EF9178E28}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="1"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="24">
-      <customFilters>
-        <customFilter operator="greaterThan" val="0"/>
-      </customFilters>
-    </filterColumn>
-  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>